--- a/dfUsuario.xlsx
+++ b/dfUsuario.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,237 +429,237 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>userid</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>grupo_intervencion</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>total_attempts</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>first_attempts_correct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>unique_steps</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>numero_sesiones_diferentes</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Tasa_exito</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>autoeficacia_general</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>progreso_inicial</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>progreso_inicial_grupo</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>numero_hints</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tasa_hints</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>selectionRating_result</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tiempo_total_segundos</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>primer_pollValue</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>prop_first_attempts_correct</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>casos</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pasos_comparacion_arriba</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>pasos_comparacion_abajo</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>casos_comparacion_arriba</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>casos_comparacion_abajo</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>performance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>performance_arriba</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>performance_abajo</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>tiempo_casos_comparacion_arriba</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>tiempo_casos_comparacion_abajo</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>porce_topicos_arriba</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>porce_topicos_abajo</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>tasa_exito_comparacion_arriba</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>autoeficacia_prom_comparacion_arriba</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>progreso_inicial_prom_comparacion_arriba</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>rating_comparacion_arriba</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>tasa_exito_comparacion_abajo</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>autoeficacia_prom_comparacion_abajo</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>progreso_inicial_prom_comparacion_abajo</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>rating_comparacion_abajo</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>proporcion_casos_comparacion</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>proporcion_steps_comparacion</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>proporcion_casos_uw</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>proporcion_steps_uw</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>proporcion_casos_dw</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>proporcion_pasos_dw</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>preferencia_casos_comparacion</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>preferencia_casos_uw</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>preferencia_steps_uw</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>preferencia_pasos_comparacion</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>tupdivtdownpasos</t>
         </is>
@@ -802,10 +814,10 @@
         <v>59.46428571428572</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4649382716049385</v>
+        <v>0.4649382716049383</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3080246913580246</v>
+        <v>0.3080246913580247</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -868,7 +880,7 @@
         <v>52.03225806451613</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6368888888888886</v>
+        <v>0.6368888888888888</v>
       </c>
       <c r="AF3" t="n">
         <v>4.911111111111111</v>
@@ -1064,7 +1076,7 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0.3833333333333334</v>
+        <v>0.3833333333333333</v>
       </c>
       <c r="J5" t="n">
         <v>0.3958333333333333</v>
@@ -1126,7 +1138,7 @@
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>0.7071428571428573</v>
+        <v>0.7071428571428572</v>
       </c>
       <c r="AF5" t="n">
         <v>4.714285714285714</v>
@@ -1810,7 +1822,7 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>0.4823913043478262</v>
+        <v>0.4823913043478261</v>
       </c>
       <c r="J11" t="n">
         <v>-1</v>
@@ -1933,7 +1945,7 @@
         <v>78.58695652173913</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5204000000000001</v>
+        <v>0.5204</v>
       </c>
       <c r="J12" t="n">
         <v>-1</v>
@@ -2305,7 +2317,7 @@
         <v>0.3271428571428571</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3700000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="K15" t="n">
         <v>18</v>
@@ -2970,7 +2982,7 @@
         <v>0.5721276595744681</v>
       </c>
       <c r="J20" t="n">
-        <v>0.330851063829787</v>
+        <v>0.3308510638297872</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
@@ -3033,7 +3045,7 @@
         <v>100</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.7231250000000002</v>
+        <v>0.723125</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -3104,7 +3116,7 @@
         <v>67.13907284768212</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5701769911504426</v>
+        <v>0.5701769911504425</v>
       </c>
       <c r="J21" t="n">
         <v>-1</v>
@@ -3229,7 +3241,7 @@
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="J22" t="n">
         <v>-1</v>
@@ -3846,7 +3858,7 @@
         <v>33.88888888888889</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="J27" t="n">
         <v>-1</v>
@@ -3971,7 +3983,7 @@
         <v>97.70212765957447</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5865625000000002</v>
+        <v>0.5865625</v>
       </c>
       <c r="J28" t="n">
         <v>-1</v>
@@ -4338,7 +4350,7 @@
         <v>45.19444444444444</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3929032258064515</v>
+        <v>0.3929032258064516</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -4463,7 +4475,7 @@
         <v>65.32142857142857</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2803571428571428</v>
+        <v>0.2803571428571429</v>
       </c>
       <c r="J32" t="n">
         <v>-1</v>
@@ -5330,7 +5342,7 @@
         <v>63.1</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4789999999999999</v>
+        <v>0.479</v>
       </c>
       <c r="J39" t="n">
         <v>-1</v>
@@ -6298,7 +6310,7 @@
         <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>0.546190476190476</v>
+        <v>0.5461904761904762</v>
       </c>
       <c r="J47" t="n">
         <v>-1</v>
@@ -6665,7 +6677,7 @@
         <v>18.83333333333333</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6233333333333333</v>
+        <v>0.6233333333333334</v>
       </c>
       <c r="J50" t="n">
         <v>-1</v>
@@ -6790,7 +6802,7 @@
         <v>99.57142857142857</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="J51" t="n">
         <v>-1</v>
@@ -6915,7 +6927,7 @@
         <v>58.14705882352941</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4232352941176472</v>
+        <v>0.4232352941176471</v>
       </c>
       <c r="J52" t="n">
         <v>-1</v>
@@ -7163,7 +7175,7 @@
         <v>53.3</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3489743589743591</v>
+        <v>0.348974358974359</v>
       </c>
       <c r="J54" t="n">
         <v>-1</v>
@@ -8736,7 +8748,7 @@
         <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5757142857142856</v>
+        <v>0.5757142857142857</v>
       </c>
       <c r="J67" t="n">
         <v>-1</v>
@@ -8864,7 +8876,7 @@
         <v>0.3656521739130435</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6021739130434781</v>
+        <v>0.6021739130434782</v>
       </c>
       <c r="K68" t="n">
         <v>30</v>
@@ -8998,10 +9010,10 @@
         <v>29.88607594936709</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4628571428571427</v>
+        <v>0.4628571428571429</v>
       </c>
       <c r="J69" t="n">
-        <v>0.3785714285714283</v>
+        <v>0.3785714285714286</v>
       </c>
       <c r="K69" t="n">
         <v>71</v>
@@ -9064,7 +9076,7 @@
         <v>35.12121212121212</v>
       </c>
       <c r="AE69" t="n">
-        <v>0.7169696969696971</v>
+        <v>0.7169696969696969</v>
       </c>
       <c r="AF69" t="n">
         <v>4.925925925925926</v>
@@ -9143,10 +9155,10 @@
         <v>85.05263157894737</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5249999999999999</v>
+        <v>0.525</v>
       </c>
       <c r="J70" t="n">
-        <v>0.4542105263157894</v>
+        <v>0.4542105263157895</v>
       </c>
       <c r="K70" t="n">
         <v>4</v>
@@ -9209,7 +9221,7 @@
         <v>82.26086956521739</v>
       </c>
       <c r="AE70" t="n">
-        <v>0.7043478260869567</v>
+        <v>0.7043478260869565</v>
       </c>
       <c r="AF70" t="n">
         <v>5</v>
@@ -9288,10 +9300,10 @@
         <v>34.90476190476191</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3595238095238096</v>
+        <v>0.3595238095238095</v>
       </c>
       <c r="J71" t="n">
-        <v>0.4507142857142856</v>
+        <v>0.4507142857142857</v>
       </c>
       <c r="K71" t="n">
         <v>75</v>
@@ -9436,7 +9448,7 @@
         <v>0.4224528301886792</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5454716981132077</v>
+        <v>0.5454716981132075</v>
       </c>
       <c r="K72" t="n">
         <v>22</v>
@@ -9835,7 +9847,7 @@
         <v>0.25</v>
       </c>
       <c r="J75" t="n">
-        <v>0.6999999999999998</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="K75" t="n">
         <v>11</v>
@@ -10238,7 +10250,7 @@
         <v>0.6744444444444445</v>
       </c>
       <c r="J78" t="n">
-        <v>0.461111111111111</v>
+        <v>0.4611111111111111</v>
       </c>
       <c r="K78" t="n">
         <v>8</v>
@@ -10301,7 +10313,7 @@
         <v>100</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.772105263157895</v>
+        <v>0.7721052631578948</v>
       </c>
       <c r="AF78" t="n">
         <v>4.6</v>
@@ -10741,7 +10753,7 @@
         <v>46.28571428571428</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5133333333333334</v>
+        <v>0.5133333333333333</v>
       </c>
       <c r="J82" t="n">
         <v>0.4899999999999999</v>
@@ -11257,7 +11269,7 @@
         <v>62</v>
       </c>
       <c r="I86" t="n">
-        <v>0.5496000000000002</v>
+        <v>0.5496</v>
       </c>
       <c r="J86" t="n">
         <v>0.4568</v>
@@ -11323,7 +11335,7 @@
         <v>58</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.7546153846153848</v>
+        <v>0.7546153846153847</v>
       </c>
       <c r="AF86" t="n">
         <v>4</v>
@@ -11540,7 +11552,7 @@
         <v>0.25</v>
       </c>
       <c r="J88" t="n">
-        <v>0.4220000000000001</v>
+        <v>0.422</v>
       </c>
       <c r="K88" t="n">
         <v>27</v>
@@ -11956,10 +11968,10 @@
         <v>87.89247311827957</v>
       </c>
       <c r="I91" t="n">
-        <v>0.4206451612903229</v>
+        <v>0.4206451612903225</v>
       </c>
       <c r="J91" t="n">
-        <v>0.3950537634408606</v>
+        <v>0.3950537634408602</v>
       </c>
       <c r="K91" t="n">
         <v>69</v>
@@ -12034,7 +12046,7 @@
         <v>86.03703703703704</v>
       </c>
       <c r="AI91" t="n">
-        <v>0.274074074074074</v>
+        <v>0.2740740740740741</v>
       </c>
       <c r="AJ91" t="n">
         <v>5</v>
@@ -12221,7 +12233,7 @@
         <v>0.25</v>
       </c>
       <c r="J93" t="n">
-        <v>0.5579999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K93" t="n">
         <v>4</v>
@@ -12495,7 +12507,7 @@
         <v>0.5573684210526316</v>
       </c>
       <c r="J95" t="n">
-        <v>0.4313157894736845</v>
+        <v>0.4313157894736842</v>
       </c>
       <c r="K95" t="n">
         <v>21</v>
@@ -12558,7 +12570,7 @@
         <v>87.47619047619048</v>
       </c>
       <c r="AE95" t="n">
-        <v>0.7452380952380955</v>
+        <v>0.7452380952380953</v>
       </c>
       <c r="AF95" t="n">
         <v>4.444444444444445</v>
@@ -12637,7 +12649,7 @@
         <v>96.78703703703704</v>
       </c>
       <c r="I96" t="n">
-        <v>0.5173809523809522</v>
+        <v>0.5173809523809524</v>
       </c>
       <c r="J96" t="n">
         <v>0.3983333333333333</v>
@@ -12703,7 +12715,7 @@
         <v>98.06451612903226</v>
       </c>
       <c r="AE96" t="n">
-        <v>0.6122580645161286</v>
+        <v>0.6122580645161291</v>
       </c>
       <c r="AF96" t="n">
         <v>5</v>
@@ -13019,7 +13031,7 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="J99" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="K99" t="n">
         <v>31</v>
@@ -13552,7 +13564,7 @@
         <v>21.58333333333333</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2549999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="J103" t="n">
         <v>0.4258333333333333</v>
@@ -13933,10 +13945,10 @@
         <v>80.92592592592592</v>
       </c>
       <c r="I106" t="n">
-        <v>0.4575862068965517</v>
+        <v>0.4575862068965518</v>
       </c>
       <c r="J106" t="n">
-        <v>0.2831034482758619</v>
+        <v>0.2831034482758621</v>
       </c>
       <c r="K106" t="n">
         <v>30</v>
@@ -13999,7 +14011,7 @@
         <v>96.57142857142857</v>
       </c>
       <c r="AE106" t="n">
-        <v>0.6799999999999998</v>
+        <v>0.68</v>
       </c>
       <c r="AF106" t="n">
         <v>4.769230769230769</v>
@@ -14693,10 +14705,10 @@
         <v>63.46428571428572</v>
       </c>
       <c r="I112" t="n">
-        <v>0.590892857142857</v>
+        <v>0.5908928571428572</v>
       </c>
       <c r="J112" t="n">
-        <v>0.4337500000000004</v>
+        <v>0.43375</v>
       </c>
       <c r="K112" t="n">
         <v>31</v>
@@ -14759,7 +14771,7 @@
         <v>73.89189189189189</v>
       </c>
       <c r="AE112" t="n">
-        <v>0.7659459459459457</v>
+        <v>0.7659459459459459</v>
       </c>
       <c r="AF112" t="n">
         <v>5</v>
@@ -14841,7 +14853,7 @@
         <v>0.25</v>
       </c>
       <c r="J113" t="n">
-        <v>0.4930769230769231</v>
+        <v>0.493076923076923</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -15112,10 +15124,10 @@
         <v>71.31818181818181</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4333333333333335</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="J115" t="n">
-        <v>0.5263636363636365</v>
+        <v>0.5263636363636364</v>
       </c>
       <c r="K115" t="n">
         <v>64</v>
@@ -15178,7 +15190,7 @@
         <v>73.18181818181819</v>
       </c>
       <c r="AE115" t="n">
-        <v>0.7636363636363636</v>
+        <v>0.7636363636363637</v>
       </c>
       <c r="AF115" t="n">
         <v>4.8</v>
@@ -15658,10 +15670,10 @@
         <v>100</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4663636363636365</v>
+        <v>0.4663636363636364</v>
       </c>
       <c r="J119" t="n">
-        <v>0.4281818181818181</v>
+        <v>0.4281818181818182</v>
       </c>
       <c r="K119" t="n">
         <v>11</v>
@@ -17253,10 +17265,10 @@
         <v>59.7</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5149473684210528</v>
+        <v>0.5149473684210526</v>
       </c>
       <c r="J132" t="n">
-        <v>0.4123157894736839</v>
+        <v>0.4123157894736842</v>
       </c>
       <c r="K132" t="n">
         <v>58</v>
@@ -17319,7 +17331,7 @@
         <v>64.73999999999999</v>
       </c>
       <c r="AE132" t="n">
-        <v>0.7287999999999998</v>
+        <v>0.7288</v>
       </c>
       <c r="AF132" t="n">
         <v>4.895833333333333</v>
@@ -17689,7 +17701,7 @@
         <v>0.25</v>
       </c>
       <c r="J135" t="n">
-        <v>0.5433333333333332</v>
+        <v>0.5433333333333333</v>
       </c>
       <c r="K135" t="n">
         <v>5</v>
@@ -17823,7 +17835,7 @@
         <v>100</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3766666666666666</v>
+        <v>0.3766666666666667</v>
       </c>
       <c r="J136" t="n">
         <v>0.3911111111111111</v>
@@ -18105,7 +18117,7 @@
         <v>44.44117647058823</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5470370370370371</v>
+        <v>0.547037037037037</v>
       </c>
       <c r="J138" t="n">
         <v>0.327037037037037</v>
@@ -18242,10 +18254,10 @@
         <v>59.28767123287671</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4482191780821916</v>
+        <v>0.4482191780821917</v>
       </c>
       <c r="J139" t="n">
-        <v>0.4302739726027401</v>
+        <v>0.4302739726027398</v>
       </c>
       <c r="K139" t="n">
         <v>66</v>
@@ -18308,7 +18320,7 @@
         <v>59.55172413793103</v>
       </c>
       <c r="AE139" t="n">
-        <v>0.6689655172413794</v>
+        <v>0.6689655172413793</v>
       </c>
       <c r="AF139" t="n">
         <v>5</v>
@@ -18320,7 +18332,7 @@
         <v>53.32</v>
       </c>
       <c r="AI139" t="n">
-        <v>0.2800000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="AJ139" t="n">
         <v>5</v>
@@ -18641,10 +18653,10 @@
         <v>29.05</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4739999999999999</v>
+        <v>0.474</v>
       </c>
       <c r="J142" t="n">
-        <v>0.4015000000000001</v>
+        <v>0.4015</v>
       </c>
       <c r="K142" t="n">
         <v>21</v>
@@ -18707,7 +18719,7 @@
         <v>22.28571428571428</v>
       </c>
       <c r="AE142" t="n">
-        <v>0.732857142857143</v>
+        <v>0.7328571428571429</v>
       </c>
       <c r="AF142" t="n">
         <v>3.571428571428572</v>
@@ -19657,10 +19669,10 @@
         <v>54.8695652173913</v>
       </c>
       <c r="I150" t="n">
-        <v>0.5386956521739129</v>
+        <v>0.538695652173913</v>
       </c>
       <c r="J150" t="n">
-        <v>0.436086956521739</v>
+        <v>0.4360869565217391</v>
       </c>
       <c r="K150" t="n">
         <v>36</v>
@@ -19802,10 +19814,10 @@
         <v>76.3225806451613</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4070370370370372</v>
+        <v>0.407037037037037</v>
       </c>
       <c r="J151" t="n">
-        <v>0.3674074074074076</v>
+        <v>0.3674074074074074</v>
       </c>
       <c r="K151" t="n">
         <v>27</v>
@@ -19868,7 +19880,7 @@
         <v>74.25</v>
       </c>
       <c r="AE151" t="n">
-        <v>0.6224999999999998</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="AF151" t="n">
         <v>5</v>
@@ -19947,10 +19959,10 @@
         <v>66.91666666666667</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5170129870129865</v>
+        <v>0.517012987012987</v>
       </c>
       <c r="J152" t="n">
-        <v>0.3202597402597405</v>
+        <v>0.3202597402597402</v>
       </c>
       <c r="K152" t="n">
         <v>74</v>
@@ -20013,7 +20025,7 @@
         <v>68.14</v>
       </c>
       <c r="AE152" t="n">
-        <v>0.6613999999999999</v>
+        <v>0.6614</v>
       </c>
       <c r="AF152" t="n">
         <v>5</v>
@@ -20922,7 +20934,7 @@
         <v>0.45</v>
       </c>
       <c r="J160" t="n">
-        <v>0.5100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="K160" t="n">
         <v>22</v>
@@ -21413,10 +21425,10 @@
         <v>72.61538461538461</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5621875000000002</v>
+        <v>0.5621875000000001</v>
       </c>
       <c r="J164" t="n">
-        <v>0.4068750000000002</v>
+        <v>0.406875</v>
       </c>
       <c r="K164" t="n">
         <v>10</v>
@@ -21479,7 +21491,7 @@
         <v>74.25</v>
       </c>
       <c r="AE164" t="n">
-        <v>0.7495000000000003</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="AF164" t="n">
         <v>4.947368421052632</v>
@@ -21558,7 +21570,7 @@
         <v>39.75</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3812499999999999</v>
+        <v>0.38125</v>
       </c>
       <c r="J165" t="n">
         <v>-1</v>
@@ -21681,7 +21693,7 @@
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
-        <v>0.4446153846153847</v>
+        <v>0.4446153846153846</v>
       </c>
       <c r="J166" t="n">
         <v>-1</v>
@@ -22179,7 +22191,7 @@
         <v>61.25</v>
       </c>
       <c r="I170" t="n">
-        <v>0.4083333333333333</v>
+        <v>0.4083333333333334</v>
       </c>
       <c r="J170" t="n">
         <v>0.4741666666666666</v>
@@ -22556,7 +22568,7 @@
       </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
-        <v>0.3384782608695653</v>
+        <v>0.3384782608695652</v>
       </c>
       <c r="J173" t="n">
         <v>-1</v>
@@ -22792,7 +22804,7 @@
       </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
-        <v>0.3612727272727274</v>
+        <v>0.3612727272727273</v>
       </c>
       <c r="J175" t="n">
         <v>-1</v>
@@ -23268,7 +23280,7 @@
         <v>78.33333333333333</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3149999999999999</v>
+        <v>0.315</v>
       </c>
       <c r="J179" t="n">
         <v>0.245</v>
